--- a/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD25"/>
+  <dimension ref="A1:BD37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,23 +750,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M2" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="N2" t="n">
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>-14</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -789,48 +785,24 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-5.164333814333816</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.484286391936251</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-10252981.10516635</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-4.164734488509126</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-17775525.49302549</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>-1.45983645983646</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-0.6604456138035775</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>1.576707551707557</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-6.194454174041624</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.705998381445838</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-6.732371332371315</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-1.057142857142857</v>
-      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -838,23 +810,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45523.5625</v>
       </c>
       <c r="C3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -876,22 +848,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -914,25 +886,49 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>-2.810695946142172</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.3289530788729875</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.4832535885167468</v>
+      </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>-4.315789473684205</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-2.961722488038305</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.282296650717704</v>
+      </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>-3.786505031539363</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>-7.175993150421064</v>
+      </c>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>-3.790743114415847</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-14238755.98086124</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-6.066985645933002</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-9872556.767507855</v>
+      </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -940,11 +936,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C4" t="n">
         <v>122</v>
@@ -953,10 +949,10 @@
         <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -978,22 +974,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N4" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="O4" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1016,48 +1012,48 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>0.9951930095850265</v>
+      </c>
       <c r="AL4" t="n">
-        <v>2.457192807192811</v>
+        <v>-0.7425846624303973</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.571965161941478</v>
+        <v>-1.00207336523126</v>
       </c>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>2439738.514991439</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>-5.072408293460938</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>0.06066629166099347</v>
+        <v>2.020680489101551</v>
       </c>
       <c r="AR4" t="n">
-        <v>5733461.53846154</v>
+        <v>-1.039287612971819</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>-0.4130869130869108</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.09029095052351943</v>
-      </c>
+        <v>-5.939976683933111</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>-0.8168831168830764</v>
-      </c>
+      <c r="AX4" t="n">
+        <v>-4.836320127073307</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>2.230986496626883</v>
+        <v>1.169535409136103</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1.892686790564774</v>
+        <v>-17531132.37639553</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.974775224775215</v>
+        <v>-6.426209463051578</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.2088911088911092</v>
+        <v>-11163972.53412044</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1066,23 +1062,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C5" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5" t="n">
         <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1104,22 +1100,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M5" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="N5" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1143,78 +1139,54 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>-4.802013503737655</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2.216033929101059</v>
-      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-10312328.29628038</v>
-      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>-4.91281078074671</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-26986994.8155293</v>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>-2.074246443211962</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.4784385861448541</v>
-      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>2.233313238485607</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-3.992667748950026</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.9129408655392979</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-6.982481311791645</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.6159754039064382</v>
-      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D6" t="n">
         <v>82</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
       </c>
       <c r="H6" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1226,27 +1198,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20</v>
-      </c>
-      <c r="O6" t="n">
-        <v>20</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1269,48 +1233,24 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>4.949450549450546</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-3.678316302919569</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>9257758.21313414</v>
-      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>2.476389512560786</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>23511598.4015984</v>
-      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>-0.2617382617382553</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.2989265336537459</v>
-      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="n">
-        <v>-2.083541458541504</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.482086524028134</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.1711010110361855</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.757792207792207</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.6027722277722278</v>
-      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
@@ -1318,29 +1258,29 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D7" t="n">
         <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
       </c>
       <c r="H7" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1352,36 +1292,28 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -1399,48 +1331,24 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="n">
-        <v>-1.913908313908323</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.8114240475862573</v>
-      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>-177301.4240884227</v>
-      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>-0.6802525465986946</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-4612195.027195025</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>-0.3043123543123514</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.04994299550319625</v>
-      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="n">
-        <v>0.4829059829060327</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>-1.271078609857867</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>-0.3495941584737636</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-1.629836829836819</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-0.2757187257187257</v>
-      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1448,29 +1356,29 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
       </c>
       <c r="H8" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1482,27 +1390,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="N8" t="n">
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-2</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1525,48 +1429,24 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="n">
-        <v>-7.280640623744077</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.264482465313932</v>
-      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>-14916806.106623</v>
-      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>-8.406158186499994</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-32760619.35669695</v>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="n">
-        <v>-1.750888192267496</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-0.5801365275515582</v>
-      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>1.246507515473013</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-6.576187604175587</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-1.314239857358761</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-9.70046754012273</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1.227615679339817</v>
-      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
@@ -1574,29 +1454,29 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D9" t="n">
         <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
       </c>
       <c r="H9" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1608,27 +1488,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>168</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-1</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1676,32 +1548,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C10" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
       </c>
       <c r="H10" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1710,27 +1582,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="M10" t="n">
-        <v>185</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1778,32 +1642,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45522.5625</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1812,20 +1676,20 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="M11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1854,25 +1718,49 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AK11" t="n">
+        <v>-2.190331058327224</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1014791165624498</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.226767676767677</v>
+      </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>2.718686868686873</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.180303030303037</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.5737373737373765</v>
+      </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>2.657920599444552</v>
+      </c>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-0.08165470222270699</v>
+      </c>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>1.608535002389402</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6210770.202020203</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.947979797979784</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2883713.99026332</v>
+      </c>
       <c r="BD11" t="n">
         <v>0</v>
       </c>
@@ -1880,32 +1768,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45522.5625</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
       </c>
       <c r="H12" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1914,23 +1802,27 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>-16</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+        <v>-16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-4</v>
+      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -1952,58 +1844,82 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AK12" t="n">
+        <v>-1.371971113681642</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.5173268349584139</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.5923444976076553</v>
+      </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>-5.377990430622006</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.343301435406659</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.76722488038277</v>
+      </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>-3.831818067410168</v>
+      </c>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>-5.536583691649483</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>1.23866634096899</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-27701244.01913876</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-7.235645933014354</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-10453359.60646322</v>
+      </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45521.65625</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
         <v>82</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>77</v>
       </c>
       <c r="H13" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -2012,23 +1928,27 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="M13" t="n">
-        <v>185</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2050,25 +1970,49 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AK13" t="n">
+        <v>0.540167195253737</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.3495274414966798</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.5933014354066981</v>
+      </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>5.129665071770347</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-2.05358851674643</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.2990430622009583</v>
+      </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>5.162915055304524</v>
+      </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>4.265605640551811</v>
+      </c>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>-2.406561904122697</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>23971578.94736842</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.080861244019133</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11778601.4864682</v>
+      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
@@ -2076,32 +2020,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45521.65625</v>
       </c>
       <c r="C14" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>77</v>
       </c>
       <c r="H14" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -2110,23 +2054,27 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2148,25 +2096,49 @@
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>-0.02724519992255026</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.06399697561151907</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.2405103668261559</v>
+      </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>-2.277458798511404</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.932323232323256</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.2014885699096212</v>
+      </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>-2.349946863083147</v>
+      </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-1.564624014711725</v>
+      </c>
       <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>0.4193682394673885</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-4255358.851674641</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-1.242264752791058</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-1066308.033995932</v>
+      </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
@@ -2174,32 +2146,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C15" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="G15" t="n">
         <v>77</v>
       </c>
       <c r="H15" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2208,21 +2180,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>185</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
@@ -2272,32 +2240,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="G16" t="n">
         <v>77</v>
       </c>
       <c r="H16" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2306,14 +2274,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="M16" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -2366,51 +2334,55 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>77</v>
       </c>
       <c r="H17" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>186</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>60</v>
-      </c>
-      <c r="M17" t="n">
-        <v>185</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
@@ -2418,8 +2390,12 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2460,32 +2436,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="G18" t="n">
         <v>77</v>
       </c>
       <c r="H18" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2494,20 +2470,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="M18" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N18" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -2558,32 +2534,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45521.5625</v>
       </c>
       <c r="C19" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D19" t="n">
         <v>82</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
         <v>77</v>
       </c>
       <c r="H19" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2592,19 +2568,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M19" t="n">
-        <v>185</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1</v>
+      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -2652,14 +2636,14 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45521.5625</v>
       </c>
       <c r="C20" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" t="n">
         <v>82</v>
@@ -2668,16 +2652,16 @@
         <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
         <v>77</v>
       </c>
       <c r="H20" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2686,26 +2670,26 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>138</v>
       </c>
       <c r="M20" t="n">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>-19</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2728,25 +2712,49 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AK20" t="n">
+        <v>-1.186023130829689</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.5727809719707877</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1.272966507177033</v>
+      </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>-6.949760765550238</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.757894736842076</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-1.903588516746407</v>
+      </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>-6.905112016703498</v>
+      </c>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-8.531978387439779</v>
+      </c>
       <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
-      <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>2.126020242478489</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-33028480.86124402</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-9.489473684210523</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-16588299.86466141</v>
+      </c>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
@@ -2754,32 +2762,32 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45520.64583333334</v>
       </c>
       <c r="C21" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" t="n">
         <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="G21" t="n">
         <v>77</v>
       </c>
       <c r="H21" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2788,20 +2796,20 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="M21" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -2810,8 +2818,12 @@
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -2852,23 +2864,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45516.65625</v>
       </c>
       <c r="C22" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" t="n">
         <v>82</v>
       </c>
       <c r="E22" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
         <v>77</v>
@@ -2890,15 +2902,23 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="M22" t="n">
-        <v>185</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -2946,23 +2966,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45516.54166666666</v>
       </c>
       <c r="C23" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="G23" t="n">
         <v>77</v>
@@ -2984,15 +3004,23 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="M23" t="n">
-        <v>185</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -3040,23 +3068,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45515.67708333334</v>
       </c>
       <c r="C24" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D24" t="n">
         <v>82</v>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="G24" t="n">
         <v>77</v>
@@ -3078,13 +3106,17 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>185</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
@@ -3134,23 +3166,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45507.54166666666</v>
+        <v>45515.65625</v>
       </c>
       <c r="C25" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" t="n">
         <v>82</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="G25" t="n">
         <v>77</v>
@@ -3172,13 +3204,17 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M25" t="n">
-        <v>185</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
@@ -3225,6 +3261,1158 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C26" t="n">
+        <v>125</v>
+      </c>
+      <c r="D26" t="n">
+        <v>82</v>
+      </c>
+      <c r="E26" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" t="n">
+        <v>153</v>
+      </c>
+      <c r="G26" t="n">
+        <v>77</v>
+      </c>
+      <c r="H26" t="n">
+        <v>773</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>159</v>
+      </c>
+      <c r="M26" t="n">
+        <v>186</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C27" t="n">
+        <v>125</v>
+      </c>
+      <c r="D27" t="n">
+        <v>82</v>
+      </c>
+      <c r="E27" t="n">
+        <v>93</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>77</v>
+      </c>
+      <c r="H27" t="n">
+        <v>773</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>159</v>
+      </c>
+      <c r="M27" t="n">
+        <v>186</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C28" t="n">
+        <v>125</v>
+      </c>
+      <c r="D28" t="n">
+        <v>82</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" t="n">
+        <v>69</v>
+      </c>
+      <c r="G28" t="n">
+        <v>77</v>
+      </c>
+      <c r="H28" t="n">
+        <v>773</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>63</v>
+      </c>
+      <c r="M28" t="n">
+        <v>186</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C29" t="n">
+        <v>125</v>
+      </c>
+      <c r="D29" t="n">
+        <v>81</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>58</v>
+      </c>
+      <c r="G29" t="n">
+        <v>77</v>
+      </c>
+      <c r="H29" t="n">
+        <v>773</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>60</v>
+      </c>
+      <c r="M29" t="n">
+        <v>186</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C30" t="n">
+        <v>125</v>
+      </c>
+      <c r="D30" t="n">
+        <v>82</v>
+      </c>
+      <c r="E30" t="n">
+        <v>46</v>
+      </c>
+      <c r="F30" t="n">
+        <v>193</v>
+      </c>
+      <c r="G30" t="n">
+        <v>77</v>
+      </c>
+      <c r="H30" t="n">
+        <v>773</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>159</v>
+      </c>
+      <c r="M30" t="n">
+        <v>186</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C31" t="n">
+        <v>125</v>
+      </c>
+      <c r="D31" t="n">
+        <v>82</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>106</v>
+      </c>
+      <c r="G31" t="n">
+        <v>77</v>
+      </c>
+      <c r="H31" t="n">
+        <v>773</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>157</v>
+      </c>
+      <c r="M31" t="n">
+        <v>186</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C32" t="n">
+        <v>125</v>
+      </c>
+      <c r="D32" t="n">
+        <v>82</v>
+      </c>
+      <c r="E32" t="n">
+        <v>78</v>
+      </c>
+      <c r="F32" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" t="n">
+        <v>77</v>
+      </c>
+      <c r="H32" t="n">
+        <v>773</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>138</v>
+      </c>
+      <c r="M32" t="n">
+        <v>186</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C33" t="n">
+        <v>125</v>
+      </c>
+      <c r="D33" t="n">
+        <v>82</v>
+      </c>
+      <c r="E33" t="n">
+        <v>56</v>
+      </c>
+      <c r="F33" t="n">
+        <v>43</v>
+      </c>
+      <c r="G33" t="n">
+        <v>77</v>
+      </c>
+      <c r="H33" t="n">
+        <v>773</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>75</v>
+      </c>
+      <c r="M33" t="n">
+        <v>186</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C34" t="n">
+        <v>125</v>
+      </c>
+      <c r="D34" t="n">
+        <v>82</v>
+      </c>
+      <c r="E34" t="n">
+        <v>134</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77</v>
+      </c>
+      <c r="H34" t="n">
+        <v>773</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>159</v>
+      </c>
+      <c r="M34" t="n">
+        <v>186</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45508.54166666666</v>
+      </c>
+      <c r="C35" t="n">
+        <v>125</v>
+      </c>
+      <c r="D35" t="n">
+        <v>82</v>
+      </c>
+      <c r="E35" t="n">
+        <v>86</v>
+      </c>
+      <c r="F35" t="n">
+        <v>35</v>
+      </c>
+      <c r="G35" t="n">
+        <v>77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>773</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>159</v>
+      </c>
+      <c r="M35" t="n">
+        <v>186</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C36" t="n">
+        <v>125</v>
+      </c>
+      <c r="D36" t="n">
+        <v>82</v>
+      </c>
+      <c r="E36" t="n">
+        <v>141</v>
+      </c>
+      <c r="F36" t="n">
+        <v>199</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77</v>
+      </c>
+      <c r="H36" t="n">
+        <v>773</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>159</v>
+      </c>
+      <c r="M36" t="n">
+        <v>186</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C37" t="n">
+        <v>125</v>
+      </c>
+      <c r="D37" t="n">
+        <v>82</v>
+      </c>
+      <c r="E37" t="n">
+        <v>85</v>
+      </c>
+      <c r="F37" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" t="n">
+        <v>77</v>
+      </c>
+      <c r="H37" t="n">
+        <v>773</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>159</v>
+      </c>
+      <c r="M37" t="n">
+        <v>186</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
@@ -495,24 +495,24 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -530,64 +530,64 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
@@ -600,107 +600,107 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -719,10 +719,10 @@
         <v>45523.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
@@ -750,18 +750,18 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="M2" t="n">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
@@ -782,27 +782,53 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>68.04278074866309</v>
+      </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>6.640485751307722</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.2942351143008999</v>
+      </c>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>26316441.30449229</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>8.917128189413802</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>0.8078586605513181</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.410778841042003</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12028605.38995147</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.089746145667178</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.42765483785222</v>
+      </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>-0.9420320676891656</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.7171384901648059</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.5459072484189291</v>
+      </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -817,10 +843,10 @@
         <v>45523.5625</v>
       </c>
       <c r="C3" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
         <v>40</v>
@@ -848,19 +874,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="N3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="O3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -887,47 +913,47 @@
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-2.810695946142172</v>
+        <v>-6.666770909846989</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.3289530788729875</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.4832535885167468</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-1.498409090909089</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>-13708465.90909091</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-4.315789473684205</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2.961722488038305</v>
-      </c>
+        <v>-3.813873325547235</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-1.282296650717704</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+        <v>-4.073759063802555</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-3.287045454545449</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-10562602.41412975</v>
+      </c>
       <c r="AU3" t="n">
-        <v>-3.786505031539363</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>-5.978863636363627</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-4.162045454545449</v>
+      </c>
       <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-7.175993150421064</v>
-      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>-3.790743114415847</v>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-14238755.98086124</v>
+        <v>-2.261515800624494</v>
       </c>
       <c r="BB3" t="n">
-        <v>-6.066985645933002</v>
+        <v>-0.5097727272727273</v>
       </c>
       <c r="BC3" t="n">
-        <v>-9872556.767507855</v>
+        <v>-0.3257067847611326</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -943,13 +969,13 @@
         <v>45522.65625</v>
       </c>
       <c r="C4" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
         <v>202</v>
@@ -974,22 +1000,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="M4" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="N4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="O4" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="P4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1013,47 +1039,47 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>0.9951930095850265</v>
+        <v>-5.733964776044502</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.7425846624303973</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1.00207336523126</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>-1.088636363636361</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>-18640000</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-5.072408293460938</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.020680489101551</v>
-      </c>
+        <v>-6.257788860644467</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>-1.039287612971819</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>0.7349502608661851</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.419886363636294</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-13505627.90843017</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-5.939976683933111</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+        <v>-6.702840909090895</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-5.069886363636357</v>
+      </c>
       <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>-4.836320127073307</v>
-      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>1.169535409136103</v>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-17531132.37639553</v>
+        <v>0.9030359248031665</v>
       </c>
       <c r="BB4" t="n">
-        <v>-6.426209463051578</v>
+        <v>-0.9857954545454541</v>
       </c>
       <c r="BC4" t="n">
-        <v>-11163972.53412044</v>
+        <v>-0.7665050068067309</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1069,13 +1095,13 @@
         <v>45522.65625</v>
       </c>
       <c r="C5" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
         <v>74</v>
@@ -1100,22 +1126,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="M5" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1136,27 +1162,53 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>66.74171122994652</v>
+      </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>8.902841571505405</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.100744284954807</v>
+      </c>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>15854971.42477406</v>
+      </c>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>7.525515764174813</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>0.7789190073646353</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.928681552365731</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>14298237.4555804</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.863662945241899</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.371477937267429</v>
+      </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>0.418222312594466</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.7714513556618818</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.7624276563694841</v>
+      </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
@@ -1164,23 +1216,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1202,10 +1254,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M6" t="n">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1258,23 +1310,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
       <c r="C7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1296,17 +1348,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>186</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
@@ -1330,25 +1378,49 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>-4.944922616898523</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.299493385871099</v>
+      </c>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>-4609838.164931045</v>
+      </c>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>-5.97127180757721</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>-5.500366320648965</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-5.247509147199594</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-2941683.127128219</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-6.015142133408389</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-6.88097382493666</v>
+      </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>0.7834117404134737</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0.1877005347593583</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.1450539938678224</v>
+      </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1356,23 +1428,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1394,17 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>186</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-1</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
@@ -1454,23 +1522,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
       <c r="C9" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F9" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -1492,14 +1560,18 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="M9" t="n">
-        <v>186</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
@@ -1521,26 +1593,52 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>67.19374999999999</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.3695790458458816</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.3389037433155089</v>
+      </c>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>2247004.512032086</v>
+      </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>0.9079894194025684</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>1.244206442043776</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.5141042780748819</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>383576.1582915769</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.951537433155096</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.614739304812815</v>
+      </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>-0.9320520145106528</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.1197860962566846</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.1189944134511529</v>
+      </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -1548,23 +1646,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -1586,15 +1684,23 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="M10" t="n">
-        <v>35</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2</v>
+      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1616,25 +1722,49 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>-2.747912194101971</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.8690656565656525</v>
+      </c>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>-588303.6616161615</v>
+      </c>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>-0.176951640729385</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>-3.580308104541672</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-3.507045454545505</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-606405.7201754248</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-1.75121212121212</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-1.69123737373738</v>
+      </c>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>-2.784582644609817</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.07590909090909093</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.1332755740636173</v>
+      </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -1649,10 +1779,10 @@
         <v>45522.5625</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1680,19 +1810,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="M11" t="n">
-        <v>182</v>
+        <v>34</v>
       </c>
       <c r="N11" t="n">
         <v>-8</v>
       </c>
       <c r="O11" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1719,47 +1849,47 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
-        <v>-2.190331058327224</v>
+        <v>0.4328779247478565</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1014791165624498</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.226767676767677</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>-0.5143716577540118</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
+        <v>7252874.331550803</v>
+      </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>2.718686868686873</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-1.180303030303037</v>
-      </c>
+        <v>3.010630475001662</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>-0.5737373737373765</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+        <v>1.889210406311122</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-1.203877005347607</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3729855.911497742</v>
+      </c>
       <c r="AU11" t="n">
-        <v>2.657920599444552</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
+        <v>2.274732620320862</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.074197860962585</v>
+      </c>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>-0.08165470222270699</v>
-      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>1.608535002389402</v>
-      </c>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>6210770.202020203</v>
+        <v>-2.066770350123548</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.947979797979784</v>
+        <v>0.2379679144385027</v>
       </c>
       <c r="BC11" t="n">
-        <v>2883713.99026332</v>
+        <v>0.1266443574924809</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -1775,13 +1905,13 @@
         <v>45522.5625</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
@@ -1806,22 +1936,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
         <v>-16</v>
       </c>
       <c r="O12" t="n">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="P12" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1845,47 +1975,47 @@
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
-        <v>-1.371971113681642</v>
+        <v>-5.58431113515968</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.5173268349584139</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-0.5923444976076553</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
+        <v>-1.320655080213903</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>-30368397.39304812</v>
+      </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="n">
-        <v>-5.377990430622006</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>2.343301435406659</v>
-      </c>
+        <v>-4.029185113685571</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
-        <v>-1.76722488038277</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
+        <v>1.97728673630715</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.270655080213913</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-12165343.01276696</v>
+      </c>
       <c r="AU12" t="n">
-        <v>-3.831818067410168</v>
-      </c>
-      <c r="AV12" t="inlineStr"/>
+        <v>-7.571390374331557</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-5.760561497326194</v>
+      </c>
       <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>-5.536583691649483</v>
-      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="n">
-        <v>1.23866634096899</v>
-      </c>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
-        <v>-27701244.01913876</v>
+        <v>-0.9825383834065029</v>
       </c>
       <c r="BB12" t="n">
-        <v>-7.235645933014354</v>
+        <v>-0.5741978609625664</v>
       </c>
       <c r="BC12" t="n">
-        <v>-10453359.60646322</v>
+        <v>-0.5566641608809968</v>
       </c>
       <c r="BD12" t="n">
         <v>1</v>
@@ -1901,10 +2031,10 @@
         <v>45521.65625</v>
       </c>
       <c r="C13" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
@@ -1932,22 +2062,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
         <v>20</v>
       </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>20</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1971,47 +2101,47 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
-        <v>0.540167195253737</v>
+        <v>4.334612890075178</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.3495274414966798</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.5933014354066981</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
+        <v>-0.4201091800356487</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
+        <v>23500448.0466429</v>
+      </c>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="n">
-        <v>5.129665071770347</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-2.05358851674643</v>
-      </c>
+        <v>5.591040922889363</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
-        <v>-0.2990430622009583</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
+        <v>-1.387046487923982</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.489100564468174</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>14102815.94335211</v>
+      </c>
       <c r="AU13" t="n">
-        <v>5.162915055304524</v>
-      </c>
-      <c r="AV13" t="inlineStr"/>
+        <v>5.090968508615575</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.320372846108143</v>
+      </c>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>4.265605640551811</v>
-      </c>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="n">
-        <v>-2.406561904122697</v>
-      </c>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>23971578.94736842</v>
+        <v>-0.09092325841835347</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.080861244019133</v>
+        <v>0.5912990196078429</v>
       </c>
       <c r="BC13" t="n">
-        <v>11778601.4864682</v>
+        <v>0.3665650338046622</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2027,10 +2157,10 @@
         <v>45521.65625</v>
       </c>
       <c r="C14" t="n">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2058,22 +2188,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2095,49 +2225,51 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>67.53779904306221</v>
+      </c>
       <c r="AK14" t="n">
-        <v>-0.02724519992255026</v>
+        <v>-1.257029460488994</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.06399697561151907</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-0.2405103668261559</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>-0.1630681818181827</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
+        <v>-3345568.181818182</v>
+      </c>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="n">
-        <v>-2.277458798511404</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.932323232323256</v>
-      </c>
+        <v>-2.323626768762622</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
-        <v>0.2014885699096212</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
+        <v>0.05417472090073261</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.01420454545456096</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-1190955.770298091</v>
+      </c>
       <c r="AU14" t="n">
-        <v>-2.349946863083147</v>
-      </c>
-      <c r="AV14" t="inlineStr"/>
+        <v>-1.356250000000003</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-1.802840909090904</v>
+      </c>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="n">
-        <v>-1.564624014711725</v>
-      </c>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="n">
-        <v>0.4193682394673885</v>
-      </c>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>-4255358.851674641</v>
+        <v>0.006451685669258467</v>
       </c>
       <c r="BB14" t="n">
-        <v>-1.242264752791058</v>
+        <v>-0.3164772727272729</v>
       </c>
       <c r="BC14" t="n">
-        <v>-1066308.033995932</v>
+        <v>-0.07699647959486788</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2153,13 +2285,13 @@
         <v>45521.64583333334</v>
       </c>
       <c r="C15" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" t="n">
         <v>178</v>
@@ -2184,15 +2316,23 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="M15" t="n">
-        <v>186</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1</v>
+      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2212,27 +2352,53 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>72.08440656565656</v>
+      </c>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>2.40815014573738</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0.3915719696969724</v>
+      </c>
       <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-171476.0890151518</v>
+      </c>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>-0.2481200292445322</v>
+      </c>
       <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-2.111835675633642</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.3889520202020265</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>167732.1259982996</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-1.129861111111126</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.3231060606060652</v>
+      </c>
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>2.578750476894065</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.05912247474747478</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.136952686001599</v>
+      </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
@@ -2247,13 +2413,13 @@
         <v>45521.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F16" t="n">
         <v>137</v>
@@ -2278,14 +2444,18 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="M16" t="n">
-        <v>186</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
@@ -2334,23 +2504,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
       <c r="C17" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
         <v>77</v>
@@ -2372,30 +2542,30 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="M17" t="n">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2408,27 +2578,53 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>80.77593582887701</v>
+      </c>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AK17" t="n">
+        <v>0.4896370535558106</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.122727272727275</v>
+      </c>
       <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>-217602.2727272725</v>
+      </c>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>-1.180634277023728</v>
+      </c>
       <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>1.853407486577538</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.457386363636374</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-87083.34236664465</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.324431818181807</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.3562499999999886</v>
+      </c>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>0.3483848550646336</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.1477272727272729</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.04562227577173239</v>
+      </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
@@ -2436,23 +2632,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
         <v>77</v>
@@ -2474,18 +2670,18 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="M18" t="n">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
@@ -2498,35 +2694,67 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>73.5529411764706</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>68.32361111111112</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>5.551435295197905</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.1240530303030276</v>
+      </c>
       <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>2406376.262626262</v>
+      </c>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>6.541808330516318</v>
+      </c>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0.6666001861737527</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.2901515151515071</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2633790.748537584</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.233017676767673</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6.735164141414145</v>
+      </c>
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>0.05847053866046181</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.4115530303030304</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.22161293970963</v>
+      </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
@@ -2541,10 +2769,10 @@
         <v>45521.5625</v>
       </c>
       <c r="C19" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
@@ -2572,23 +2800,21 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="N19" t="n">
         <v>-4</v>
       </c>
       <c r="O19" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="P19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -2609,26 +2835,52 @@
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>70.47368421052632</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-6.350351341357268</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-1.637499999999996</v>
+      </c>
       <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
+      <c r="AN19" t="n">
+        <v>-9479745.81339713</v>
+      </c>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>-5.454330823073505</v>
+      </c>
       <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>2.730100050171075</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.985616028708137</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-9296950.278093841</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-6.269108851674645</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-3.875777511961715</v>
+      </c>
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
+      <c r="BA19" t="n">
+        <v>-0.5748323743062862</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.6115131578947368</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.462664904973378</v>
+      </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
@@ -2643,13 +2895,13 @@
         <v>45521.5625</v>
       </c>
       <c r="C20" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" t="n">
         <v>63</v>
@@ -2674,22 +2926,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="M20" t="n">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="N20" t="n">
         <v>-19</v>
       </c>
       <c r="O20" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="P20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2711,49 +2963,51 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AJ20" t="n">
+        <v>65.97727272727273</v>
+      </c>
       <c r="AK20" t="n">
-        <v>-1.186023130829689</v>
+        <v>-8.228429759785669</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.5727809719707877</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>-1.272966507177033</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
+        <v>-1.695320855614973</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
+        <v>-33358871.15641712</v>
+      </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="n">
-        <v>-6.949760765550238</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.757894736842076</v>
-      </c>
+        <v>-7.329428557376104</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="n">
-        <v>-1.903588516746407</v>
-      </c>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
+        <v>1.32295656964817</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.342780748663102</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-20278688.94379877</v>
+      </c>
       <c r="AU20" t="n">
-        <v>-6.905112016703498</v>
-      </c>
-      <c r="AV20" t="inlineStr"/>
+        <v>-9.40741978609627</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-6.972727272727269</v>
+      </c>
       <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="n">
-        <v>-8.531978387439779</v>
-      </c>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="n">
-        <v>2.126020242478489</v>
-      </c>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
-        <v>-33028480.86124402</v>
+        <v>-0.4467515755119642</v>
       </c>
       <c r="BB20" t="n">
-        <v>-9.489473684210523</v>
+        <v>-1.236831550802138</v>
       </c>
       <c r="BC20" t="n">
-        <v>-16588299.86466141</v>
+        <v>-0.5178998993836745</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -2769,13 +3023,13 @@
         <v>45520.64583333334</v>
       </c>
       <c r="C21" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
         <v>153</v>
@@ -2800,63 +3054,95 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M21" t="n">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="N21" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="O21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>70.28352272727273</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-4.025781922042455</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.6675766957500748</v>
+      </c>
       <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AN21" t="n">
+        <v>-1241921.89698846</v>
+      </c>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AP21" t="n">
+        <v>-2.697567773626901</v>
+      </c>
       <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>0.2046797047954101</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.1911905432029073</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-818236.179440351</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-3.731972980579798</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-3.357444413171976</v>
+      </c>
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
+      <c r="BA21" t="n">
+        <v>-1.255358856765046</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
@@ -2871,13 +3157,13 @@
         <v>45516.65625</v>
       </c>
       <c r="C22" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>178</v>
@@ -2902,22 +3188,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="O22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2940,25 +3226,49 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
+      <c r="AK22" t="n">
+        <v>6.089047780125895</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.2040719696969688</v>
+      </c>
       <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
+      <c r="AN22" t="n">
+        <v>1979628.708964646</v>
+      </c>
       <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
+      <c r="AP22" t="n">
+        <v>5.087420648332937</v>
+      </c>
       <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>0.398779474038804</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.011931818181807</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2533885.095720999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.760795454545445</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.605934343434342</v>
+      </c>
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
+      <c r="BA22" t="n">
+        <v>0.8696428223105741</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.3035669191919192</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.22161293970963</v>
+      </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
@@ -2973,13 +3283,13 @@
         <v>45516.54166666666</v>
       </c>
       <c r="C23" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
         <v>180</v>
@@ -3004,22 +3314,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="M23" t="n">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3042,25 +3352,49 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
+      <c r="AK23" t="n">
+        <v>1.165836514289481</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-1.805113636363636</v>
+      </c>
       <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
+      <c r="AN23" t="n">
+        <v>2985852.272727273</v>
+      </c>
       <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
+      <c r="AP23" t="n">
+        <v>4.511101033142836</v>
+      </c>
       <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>2.766901967417368</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.984090909090895</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1321688.811256158</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.800568181818193</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.928409090909085</v>
+      </c>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr"/>
+      <c r="BA23" t="n">
+        <v>-3.394296391025684</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>-0.04886363636363633</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>-0.136952686001599</v>
+      </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
@@ -3075,13 +3409,13 @@
         <v>45515.67708333334</v>
       </c>
       <c r="C24" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="n">
         <v>165</v>
@@ -3106,18 +3440,18 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="M24" t="n">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
@@ -3140,25 +3474,49 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AK24" t="n">
+        <v>5.16753648914441</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-0.06076203208556308</v>
+      </c>
       <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
+      <c r="AN24" t="n">
+        <v>11219179.47860963</v>
+      </c>
       <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
+      <c r="AP24" t="n">
+        <v>3.738843781354603</v>
+      </c>
       <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>3.612489841475877</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.103810160427827</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>5037214.783328479</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.823930481283426</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>7.727606951871664</v>
+      </c>
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
+      <c r="BA24" t="n">
+        <v>0.3685337035287972</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.2759358288770055</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0.1663710649194801</v>
+      </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
@@ -3173,13 +3531,13 @@
         <v>45515.65625</v>
       </c>
       <c r="C25" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="D25" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" t="n">
         <v>187</v>
@@ -3204,19 +3562,23 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="M25" t="n">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -3238,25 +3600,49 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
+      <c r="AK25" t="n">
+        <v>-1.38937364744487</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-2.581517379679145</v>
+      </c>
       <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
+      <c r="AN25" t="n">
+        <v>-1210937.592840165</v>
+      </c>
       <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
+      <c r="AP25" t="n">
+        <v>1.727642798253868</v>
+      </c>
       <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>0.2419084777794467</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.367082590611972</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>-86104.64801171096</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>-3.242951574569247</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.610386957813432</v>
+      </c>
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
-      <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr"/>
+      <c r="BA25" t="n">
+        <v>-1.359994890304549</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0.02723559120617947</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>-0.06801543080613381</v>
+      </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
@@ -3271,10 +3657,10 @@
         <v>45515.5625</v>
       </c>
       <c r="C26" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
         <v>17</v>
@@ -3302,19 +3688,23 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -3336,25 +3726,49 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
+      <c r="AK26" t="n">
+        <v>0.02459947102754256</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-1.222188995215312</v>
+      </c>
       <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
+      <c r="AN26" t="n">
+        <v>587120.2153110052</v>
+      </c>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
+      <c r="AP26" t="n">
+        <v>0.3419504260465231</v>
+      </c>
       <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>1.909436150472288</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.600448564593307</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>402850.2249925842</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-0.1901614832535898</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.482595693779899</v>
+      </c>
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
-      <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
+      <c r="BA26" t="n">
+        <v>-0.6050718118223841</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0.04829545454545459</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0.09306774897807513</v>
+      </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
@@ -3369,13 +3783,13 @@
         <v>45515.54166666666</v>
       </c>
       <c r="C27" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" t="n">
         <v>74</v>
@@ -3400,19 +3814,23 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M27" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="O27" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -3434,25 +3852,49 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AK27" t="n">
+        <v>-3.175670678764192</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.4807486631016005</v>
+      </c>
       <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
+      <c r="AN27" t="n">
+        <v>-1459212.56684492</v>
+      </c>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="AP27" t="n">
+        <v>-1.439138831859267</v>
+      </c>
       <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>1.497366639269558</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>-1.80187165775402</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>-465633.0931885233</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-3.30828877005348</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-3.782085561497325</v>
+      </c>
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
+      <c r="BA27" t="n">
+        <v>-1.923622652973922</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>-0.04174125874125889</v>
+      </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
@@ -3467,10 +3909,10 @@
         <v>45514.67708333334</v>
       </c>
       <c r="C28" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
@@ -3498,14 +3940,18 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="M28" t="n">
-        <v>186</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
@@ -3528,25 +3974,49 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
+      <c r="AK28" t="n">
+        <v>11.42025415227688</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.6786096256684502</v>
+      </c>
       <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
+      <c r="AN28" t="n">
+        <v>33994391.71122994</v>
+      </c>
       <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
+      <c r="AP28" t="n">
+        <v>9.396166424073627</v>
+      </c>
       <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>-2.225128889783576</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>-2.316109625668474</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>14387367.21809869</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>14.18502673796792</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>12.09010695187166</v>
+      </c>
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
-      <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
+      <c r="BA28" t="n">
+        <v>0.270171146863067</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0.7219251336898393</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0.5886582085000445</v>
+      </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
@@ -3561,10 +4031,10 @@
         <v>45514.65625</v>
       </c>
       <c r="C29" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -3592,14 +4062,18 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="M29" t="n">
-        <v>186</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
@@ -3622,25 +4096,49 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
+      <c r="AK29" t="n">
+        <v>3.831704548550221</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-1.58271531100479</v>
+      </c>
       <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
+      <c r="AN29" t="n">
+        <v>3294898.325358852</v>
+      </c>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AP29" t="n">
+        <v>3.212760426337368</v>
+      </c>
       <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>3.384785940445283</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.518899521531125</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1588556.238894036</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.842882775119605</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>5.651495215311002</v>
+      </c>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
+      <c r="BA29" t="n">
+        <v>-0.02941303836112397</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0.03977272727272729</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.1616423155145981</v>
+      </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
@@ -3655,13 +4153,13 @@
         <v>45514.54166666666</v>
       </c>
       <c r="C30" t="n">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n">
         <v>193</v>
@@ -3686,19 +4184,23 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="M30" t="n">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="N30" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="O30" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-1</v>
+      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -3720,25 +4222,49 @@
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
+      <c r="AK30" t="n">
+        <v>4.497844206348788</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>-0.8820987654321009</v>
+      </c>
       <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
+      <c r="AN30" t="n">
+        <v>540479.7979797977</v>
+      </c>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
+      <c r="AP30" t="n">
+        <v>3.753297655296223</v>
+      </c>
       <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>6.529332199381685</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.015953984287364</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>882722.8283380743</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2.048995510662181</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.920179573512911</v>
+      </c>
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
+      <c r="BA30" t="n">
+        <v>1.476114748566122</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.03247474747474755</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.09343772185734411</v>
+      </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
@@ -3753,10 +4279,10 @@
         <v>45513.67708333334</v>
       </c>
       <c r="C31" t="n">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>9</v>
@@ -3784,10 +4310,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="M31" t="n">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -3814,25 +4340,49 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
+      <c r="AK31" t="n">
+        <v>5.988729129077242</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>-3.419886363636365</v>
+      </c>
       <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
+      <c r="AN31" t="n">
+        <v>6887034.090909091</v>
+      </c>
       <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
+      <c r="AP31" t="n">
+        <v>8.011850432176516</v>
+      </c>
       <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
+      <c r="AR31" t="n">
+        <v>-2.230655978170063</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.1647727272727195</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3035013.213297925</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5.821590909090915</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>8.0625</v>
+      </c>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
+      <c r="BA31" t="n">
+        <v>0.04467148514141073</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.2085227272727272</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.1930165193377336</v>
+      </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
@@ -3847,13 +4397,13 @@
         <v>45513.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="D32" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E32" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F32" t="n">
         <v>28</v>
@@ -3878,19 +4428,19 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="M32" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -3916,25 +4466,49 @@
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
+      <c r="AK32" t="n">
+        <v>6.211630004234308</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.25</v>
+      </c>
       <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
+      <c r="AN32" t="n">
+        <v>5466605.113636363</v>
+      </c>
       <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
+      <c r="AP32" t="n">
+        <v>5.923114692952453</v>
+      </c>
       <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
+      <c r="AR32" t="n">
+        <v>1.934981211672778</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>-0.7767045454545496</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2679710.199527505</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.469318181818167</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>8.40625</v>
+      </c>
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
+      <c r="BA32" t="n">
+        <v>0.6262389293239679</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0.1920454545454549</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.3998641571527601</v>
+      </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
@@ -3949,13 +4523,13 @@
         <v>45513.54166666666</v>
       </c>
       <c r="C33" t="n">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F33" t="n">
         <v>43</v>
@@ -3980,18 +4554,18 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="M33" t="n">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>5</v>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>0</v>
@@ -4014,25 +4588,49 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
+      <c r="AK33" t="n">
+        <v>6.150198322393763</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>-0.5787098930481314</v>
+      </c>
       <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
+      <c r="AN33" t="n">
+        <v>4741418.690582294</v>
+      </c>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
+      <c r="AP33" t="n">
+        <v>7.832641138358738</v>
+      </c>
       <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
+      <c r="AR33" t="n">
+        <v>1.446727699068362</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.62128639334523</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3125642.18425308</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.701552287581706</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7.521397801544865</v>
+      </c>
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
+      <c r="BA33" t="n">
+        <v>-0.3668309840014814</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0.1877005347593583</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.1450539938678224</v>
+      </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
@@ -4047,13 +4645,13 @@
         <v>45508.64583333334</v>
       </c>
       <c r="C34" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D34" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="E34" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" t="n">
         <v>9</v>
@@ -4078,14 +4676,18 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M34" t="n">
-        <v>186</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
         <v>0</v>
@@ -4141,13 +4743,13 @@
         <v>45508.54166666666</v>
       </c>
       <c r="C35" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D35" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E35" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F35" t="n">
         <v>35</v>
@@ -4172,14 +4774,18 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M35" t="n">
-        <v>186</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-1</v>
+      </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>0</v>
@@ -4235,13 +4841,13 @@
         <v>45507.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D36" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E36" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" t="n">
         <v>199</v>
@@ -4266,10 +4872,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M36" t="n">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -4329,13 +4935,13 @@
         <v>45507.54166666666</v>
       </c>
       <c r="C37" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D37" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E37" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F37" t="n">
         <v>17</v>
@@ -4360,10 +4966,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="M37" t="n">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>

--- a/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
@@ -530,74 +530,74 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -786,48 +786,48 @@
         <v>68.04278074866309</v>
       </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>6.640485751307722</v>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
+        <v>9.089746145667178</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>26316441.30449229</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10.42765483785222</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0.8078586605513181</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0.7171384901648059</v>
+      </c>
+      <c r="AT2" t="n">
         <v>-0.2942351143008999</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>26316441.30449229</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>8.917128189413802</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>0.8078586605513181</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-0.9420320676891656</v>
+      </c>
+      <c r="AW2" t="n">
         <v>4.410778841042003</v>
       </c>
-      <c r="AT2" t="n">
-        <v>12028605.38995147</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.089746145667178</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.42765483785222</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>0.5459072484189291</v>
+      </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-0.9420320676891656</v>
+        <v>6.640485751307722</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7171384901648059</v>
+        <v>8.917128189413802</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5459072484189291</v>
+        <v>12028605.38995147</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -912,48 +912,48 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
-        <v>-6.666770909846989</v>
-      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-1.498409090909089</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>-6.033030303030287</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-13744621.21212121</v>
+      </c>
       <c r="AN3" t="n">
-        <v>-13708465.90909091</v>
+        <v>-4.183636363636367</v>
       </c>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>-3.813873325547235</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>-4.073759063802555</v>
-      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-4.055434497064908</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-3.287045454545449</v>
+        <v>-0.5093939393939393</v>
       </c>
       <c r="AT3" t="n">
-        <v>-10562602.41412975</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-5.978863636363627</v>
-      </c>
+        <v>-1.495757575757573</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-4.162045454545449</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
+        <v>-2.229299625495273</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-3.216212121212152</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.3283421602552039</v>
+      </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-2.261515800624494</v>
+        <v>-6.671074826944377</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.5097727272727273</v>
+        <v>-3.890209040556869</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.3257067847611326</v>
+        <v>-10568611.85975659</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1038,48 +1038,48 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>-5.733964776044502</v>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
+        <v>-6.702840909090895</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-18640000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-5.069886363636357</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.7349502608662135</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>-0.9857954545454541</v>
+      </c>
+      <c r="AT4" t="n">
         <v>-1.088636363636361</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
-        <v>-18640000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>-6.257788860644467</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>0.7349502608661851</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>0.9030359248031665</v>
+      </c>
+      <c r="AW4" t="n">
         <v>1.419886363636294</v>
       </c>
-      <c r="AT4" t="n">
-        <v>-13505627.90843017</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-6.702840909090895</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-5.069886363636357</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>-0.7665050068067309</v>
+      </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>0.9030359248031665</v>
+        <v>-5.733964776044502</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.9857954545454541</v>
+        <v>-6.257788860644467</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.7665050068067309</v>
+        <v>-13505627.90843017</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1166,48 +1166,48 @@
         <v>66.74171122994652</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>8.902841571505405</v>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>2.100744284954807</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>7.863662945241899</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>15854971.42477406</v>
+      </c>
       <c r="AN5" t="n">
-        <v>15854971.42477406</v>
+        <v>5.371477937267429</v>
       </c>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>7.525515764174813</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
         <v>0.7789190073646353</v>
       </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
+        <v>0.7714513556618818</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.100744284954811</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0.418222312594466</v>
+      </c>
+      <c r="AW5" t="n">
         <v>-0.928681552365731</v>
       </c>
-      <c r="AT5" t="n">
-        <v>14298237.4555804</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.863662945241899</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.371477937267429</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>0.7624276563694841</v>
+      </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>0.418222312594466</v>
+        <v>8.902841571505405</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.7714513556618818</v>
+        <v>7.525515764174813</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.7624276563694841</v>
+        <v>14298237.45558041</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D6" t="n">
         <v>34</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M6" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
         <v>126</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
         <v>42</v>
@@ -1378,48 +1378,48 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>-4.944922616898523</v>
-      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
+        <v>-6.015142133408389</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-4609838.164931045</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-6.88097382493666</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-5.500366320648908</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-0.1877005347593583</v>
+      </c>
+      <c r="AT7" t="n">
         <v>1.299493385871099</v>
       </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
-        <v>-4609838.164931045</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>-5.97127180757721</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>-5.500366320648965</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0.7834117404134737</v>
+      </c>
+      <c r="AW7" t="n">
         <v>-5.247509147199594</v>
       </c>
-      <c r="AT7" t="n">
-        <v>-2941683.127128219</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-6.015142133408389</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-6.88097382493666</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>-0.1450539938678224</v>
+      </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>0.7834117404134737</v>
+        <v>-4.944922616898523</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.1877005347593583</v>
+        <v>-5.97127180757721</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.1450539938678224</v>
+        <v>-2941683.127128219</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1596,48 +1596,48 @@
       <c r="AJ9" t="n">
         <v>67.19374999999999</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0.3695790458458816</v>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
+        <v>2.951537433155096</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2247004.512032086</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.614739304812815</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>1.244206442043776</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-0.1197860962566846</v>
+      </c>
+      <c r="AT9" t="n">
         <v>0.3389037433155089</v>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>2247004.512032086</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>0.9079894194025684</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>1.244206442043776</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.5141042780748819</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>383576.1582915769</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.951537433155096</v>
-      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>1.614739304812815</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
+        <v>-0.9320520145106528</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.5141042780749103</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1189944134511529</v>
+      </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>-0.9320520145106528</v>
+        <v>0.3695790458458816</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.1197860962566846</v>
+        <v>0.9079894194025684</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.1189944134511529</v>
+        <v>383576.1582915769</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -1722,48 +1722,48 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="n">
-        <v>-2.747912194101971</v>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
+        <v>-1.75121212121212</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-588303.6616161615</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1.69123737373738</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-3.580308104541672</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-0.07590909090909093</v>
+      </c>
+      <c r="AT10" t="n">
         <v>-0.8690656565656525</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>-588303.6616161615</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>-0.176951640729385</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>-3.580308104541672</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-2.784582644609817</v>
+      </c>
+      <c r="AW10" t="n">
         <v>-3.507045454545505</v>
       </c>
-      <c r="AT10" t="n">
-        <v>-606405.7201754248</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-1.75121212121212</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-1.69123737373738</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-0.1332755740636173</v>
+      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>-2.784582644609817</v>
+        <v>-2.747912194101971</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.07590909090909093</v>
+        <v>-0.176951640729385</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.1332755740636173</v>
+        <v>-606405.7201754248</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -1848,48 +1848,48 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="n">
-        <v>0.4328779247478565</v>
-      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
+        <v>2.274732620320862</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7252874.331550803</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>3.074197860962585</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>1.889210406311065</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>0.237967914438503</v>
+      </c>
+      <c r="AT11" t="n">
         <v>-0.5143716577540118</v>
       </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
-        <v>7252874.331550803</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="n">
-        <v>3.010630475001662</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>1.889210406311122</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-2.066770350123548</v>
+      </c>
+      <c r="AW11" t="n">
         <v>-1.203877005347607</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3729855.911497742</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.274732620320862</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.074197860962585</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>0.1266443574924809</v>
+      </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>-2.066770350123548</v>
+        <v>0.4328779247478565</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.2379679144385027</v>
+        <v>3.010630475001662</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1266443574924809</v>
+        <v>3729855.911497741</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -1974,48 +1974,48 @@
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="n">
-        <v>-5.58431113515968</v>
-      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
+        <v>-7.571390374331557</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-30368397.39304812</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-5.760561497326194</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>1.97728673630715</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-0.5741978609625664</v>
+      </c>
+      <c r="AT12" t="n">
         <v>-1.320655080213903</v>
       </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="n">
-        <v>-30368397.39304812</v>
-      </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>-4.029185113685571</v>
-      </c>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="n">
-        <v>1.97728673630715</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.270655080213913</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-12165343.01276696</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-7.571390374331557</v>
-      </c>
+      <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
-        <v>-5.760561497326194</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
+        <v>-0.9825383834065065</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.270655080213885</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.556664160880997</v>
+      </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
-        <v>-0.9825383834065029</v>
+        <v>-5.58431113515968</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0.5741978609625664</v>
+        <v>-4.029185113685571</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.5566641608809968</v>
+        <v>-12165343.01276696</v>
       </c>
       <c r="BD12" t="n">
         <v>1</v>
@@ -2100,48 +2100,48 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="n">
-        <v>4.334612890075178</v>
-      </c>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
+        <v>5.090968508615575</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>23500448.0466429</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.320372846108143</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>-1.387046487923982</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0.5912990196078429</v>
+      </c>
+      <c r="AT13" t="n">
         <v>-0.4201091800356487</v>
       </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="n">
-        <v>23500448.0466429</v>
-      </c>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>5.591040922889363</v>
-      </c>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="n">
-        <v>-1.387046487923982</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>-0.09092325841835347</v>
+      </c>
+      <c r="AW13" t="n">
         <v>-1.489100564468174</v>
       </c>
-      <c r="AT13" t="n">
-        <v>14102815.94335211</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.090968508615575</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.320372846108143</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>0.366565033804662</v>
+      </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>-0.09092325841835347</v>
+        <v>4.334612890075178</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.5912990196078429</v>
+        <v>5.591040922889363</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.3665650338046622</v>
+        <v>14102815.94335211</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2228,48 +2228,48 @@
       <c r="AJ14" t="n">
         <v>67.53779904306221</v>
       </c>
-      <c r="AK14" t="n">
-        <v>-1.257029460488994</v>
-      </c>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>-0.1630681818181827</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
+        <v>-1.356250000000003</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-3345568.181818182</v>
+      </c>
       <c r="AN14" t="n">
-        <v>-3345568.181818182</v>
+        <v>-1.802840909090904</v>
       </c>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="n">
-        <v>-2.323626768762622</v>
-      </c>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="n">
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
         <v>0.05417472090073261</v>
       </c>
+      <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
+        <v>-0.3164772727272729</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.1630681818181792</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>0.006451685669258467</v>
+      </c>
+      <c r="AW14" t="n">
         <v>0.01420454545456096</v>
       </c>
-      <c r="AT14" t="n">
-        <v>-1190955.770298091</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-1.356250000000003</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>-1.802840909090904</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-0.07699647959486788</v>
+      </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>0.006451685669258467</v>
+        <v>-1.257029460488994</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.3164772727272729</v>
+        <v>-2.323626768762622</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0.07699647959486788</v>
+        <v>-1190955.770298091</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2356,48 +2356,48 @@
         <v>72.08440656565656</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="n">
-        <v>2.40815014573738</v>
-      </c>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
+        <v>-1.129861111111126</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-171476.0890151518</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.3231060606060652</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>-2.111835675633642</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-0.05912247474747478</v>
+      </c>
+      <c r="AT15" t="n">
         <v>-0.3915719696969724</v>
       </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
-        <v>-171476.0890151518</v>
-      </c>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="n">
-        <v>-0.2481200292445322</v>
-      </c>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="n">
-        <v>-2.111835675633642</v>
-      </c>
-      <c r="AS15" t="n">
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>2.578750476894065</v>
+      </c>
+      <c r="AW15" t="n">
         <v>-0.3889520202020265</v>
       </c>
-      <c r="AT15" t="n">
-        <v>167732.1259982996</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>-1.129861111111126</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-0.3231060606060652</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>0.136952686001599</v>
+      </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
-        <v>2.578750476894065</v>
+        <v>2.40815014573738</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0.05912247474747478</v>
+        <v>-0.2481200292445322</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.136952686001599</v>
+        <v>167732.1259982996</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>45521.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" t="n">
         <v>76</v>
@@ -2447,7 +2447,7 @@
         <v>196</v>
       </c>
       <c r="M16" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2582,48 +2582,48 @@
         <v>80.77593582887701</v>
       </c>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="n">
-        <v>0.4896370535558106</v>
-      </c>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
+        <v>1.324431818181807</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-217602.2727272725</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.3562499999999886</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>1.853407486577538</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.1477272727272729</v>
+      </c>
+      <c r="AT17" t="n">
         <v>3.122727272727275</v>
       </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="n">
-        <v>-217602.2727272725</v>
-      </c>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="n">
-        <v>-1.180634277023728</v>
-      </c>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="n">
-        <v>1.853407486577538</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>0.3483848550646336</v>
+      </c>
+      <c r="AW17" t="n">
         <v>-0.457386363636374</v>
       </c>
-      <c r="AT17" t="n">
-        <v>-87083.34236664465</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.324431818181807</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>-0.3562499999999886</v>
-      </c>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>0.04562227577173239</v>
+      </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
-        <v>0.3483848550646336</v>
+        <v>0.4896370535558106</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.1477272727272729</v>
+        <v>-1.180634277023728</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.04562227577173239</v>
+        <v>-87083.34236664465</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -2694,14 +2694,14 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
@@ -2712,48 +2712,48 @@
       <c r="AJ18" t="n">
         <v>68.32361111111112</v>
       </c>
-      <c r="AK18" t="n">
-        <v>5.551435295197905</v>
-      </c>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
+        <v>5.233017676767673</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2406376.262626262</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.735164141414145</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>0.6666001861737527</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>0.4115530303030304</v>
+      </c>
+      <c r="AT18" t="n">
         <v>0.1240530303030276</v>
       </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="n">
-        <v>2406376.262626262</v>
-      </c>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="n">
-        <v>6.541808330516318</v>
-      </c>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="n">
-        <v>0.6666001861737527</v>
-      </c>
-      <c r="AS18" t="n">
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>0.05847053866046181</v>
+      </c>
+      <c r="AW18" t="n">
         <v>0.2901515151515071</v>
       </c>
-      <c r="AT18" t="n">
-        <v>2633790.748537584</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.233017676767673</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6.735164141414145</v>
-      </c>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>0.22161293970963</v>
+      </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
-        <v>0.05847053866046181</v>
+        <v>5.551435295197905</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.4115530303030304</v>
+        <v>6.541808330516318</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.22161293970963</v>
+        <v>2633790.748537584</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -2836,50 +2836,50 @@
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="n">
-        <v>70.47368421052632</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>-6.350351341357268</v>
-      </c>
+        <v>70.45454545454544</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>-1.637499999999996</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
+        <v>-6.266477272727286</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-9621925.505050506</v>
+      </c>
       <c r="AN19" t="n">
-        <v>-9479745.81339713</v>
+        <v>-3.93093434343433</v>
       </c>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="n">
-        <v>-5.454330823073505</v>
-      </c>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="n">
-        <v>2.730100050171075</v>
-      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>2.800631015993559</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="n">
-        <v>1.985616028708137</v>
+        <v>-0.6259469696969695</v>
       </c>
       <c r="AT19" t="n">
-        <v>-9296950.278093841</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>-6.269108851674645</v>
-      </c>
+        <v>-1.552651515151517</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="n">
-        <v>-3.875777511961715</v>
-      </c>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
+        <v>-0.600895325968029</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.952335858585855</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.4535389413040143</v>
+      </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
-        <v>-0.5748323743062862</v>
+        <v>-6.316178798218132</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0.6115131578947368</v>
+        <v>-5.380076571829122</v>
       </c>
       <c r="BC19" t="n">
-        <v>-0.462664904973378</v>
+        <v>-9133775.147276189</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -2966,48 +2966,48 @@
       <c r="AJ20" t="n">
         <v>65.97727272727273</v>
       </c>
-      <c r="AK20" t="n">
-        <v>-8.228429759785669</v>
-      </c>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
+        <v>-9.40741978609627</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-33358871.15641712</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-6.972727272727269</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>1.32295656964817</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-1.236831550802138</v>
+      </c>
+      <c r="AT20" t="n">
         <v>-1.695320855614973</v>
       </c>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>-33358871.15641712</v>
-      </c>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="n">
-        <v>-7.329428557376104</v>
-      </c>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="n">
-        <v>1.32295656964817</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>-0.4467515755119642</v>
+      </c>
+      <c r="AW20" t="n">
         <v>1.342780748663102</v>
       </c>
-      <c r="AT20" t="n">
-        <v>-20278688.94379877</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-9.40741978609627</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>-6.972727272727269</v>
-      </c>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-0.5178998993836745</v>
+      </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
-        <v>-0.4467515755119642</v>
+        <v>-8.228429759785669</v>
       </c>
       <c r="BB20" t="n">
-        <v>-1.236831550802138</v>
+        <v>-7.329428557376104</v>
       </c>
       <c r="BC20" t="n">
-        <v>-0.5178998993836745</v>
+        <v>-20278688.94379877</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -3082,14 +3082,14 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
@@ -3100,48 +3100,48 @@
       <c r="AJ21" t="n">
         <v>70.05</v>
       </c>
-      <c r="AK21" t="n">
-        <v>-4.025781922042455</v>
-      </c>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>-0.6675766957500748</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
+        <v>-3.712834224598922</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1227760.546642899</v>
+      </c>
       <c r="AN21" t="n">
-        <v>-1241921.89698846</v>
+        <v>-3.335115864527623</v>
       </c>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="n">
-        <v>-2.697567773626901</v>
-      </c>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="n">
-        <v>0.2046797047954101</v>
-      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="n">
+        <v>0.2975194663137017</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
-        <v>0.1911905432029073</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>-818236.179440351</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>-3.731972980579798</v>
-      </c>
+        <v>-0.6808674985145586</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="n">
-        <v>-3.357444413171976</v>
-      </c>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
+        <v>-1.261373382115956</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.1329768270944101</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
-        <v>-1.255358856765046</v>
+        <v>-4.027486597145312</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>-2.739322588789406</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>-819851.9671755133</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -3226,48 +3226,48 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="n">
-        <v>6.089047780125895</v>
-      </c>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
+        <v>3.760795454545445</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1979628.708964646</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>4.605934343434342</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>0.398779474038804</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>0.3035669191919192</v>
+      </c>
+      <c r="AT22" t="n">
         <v>0.2040719696969688</v>
       </c>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="n">
-        <v>1979628.708964646</v>
-      </c>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="n">
-        <v>5.087420648332937</v>
-      </c>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="n">
-        <v>0.398779474038804</v>
-      </c>
-      <c r="AS22" t="n">
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>0.8696428223105741</v>
+      </c>
+      <c r="AW22" t="n">
         <v>1.011931818181807</v>
       </c>
-      <c r="AT22" t="n">
-        <v>2533885.095720999</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.760795454545445</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.605934343434342</v>
-      </c>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>0.22161293970963</v>
+      </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
-        <v>0.8696428223105741</v>
+        <v>6.089047780125895</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.3035669191919192</v>
+        <v>5.087420648332937</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.22161293970963</v>
+        <v>2533885.095720999</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -3352,48 +3352,48 @@
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="n">
-        <v>1.165836514289481</v>
-      </c>
+      <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
+        <v>3.800568181818193</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>2985852.272727273</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>4.928409090909085</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="n">
+        <v>2.766901967417368</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>-0.04886363636363633</v>
+      </c>
+      <c r="AT23" t="n">
         <v>-1.805113636363636</v>
       </c>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="n">
-        <v>2985852.272727273</v>
-      </c>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="n">
-        <v>4.511101033142836</v>
-      </c>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="n">
-        <v>2.766901967417368</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.984090909090895</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1321688.811256158</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.800568181818193</v>
-      </c>
+      <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="n">
-        <v>4.928409090909085</v>
-      </c>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
+        <v>-3.394296391025684</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.984090909090924</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-0.136952686001599</v>
+      </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
-        <v>-3.394296391025684</v>
+        <v>1.165836514289481</v>
       </c>
       <c r="BB23" t="n">
-        <v>-0.04886363636363633</v>
+        <v>4.511101033142836</v>
       </c>
       <c r="BC23" t="n">
-        <v>-0.136952686001599</v>
+        <v>1321688.811256158</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
@@ -3474,48 +3474,48 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="n">
-        <v>5.16753648914441</v>
-      </c>
+      <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="n">
+        <v>7.823930481283426</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>11219179.47860963</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>7.727606951871664</v>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="n">
+        <v>3.612489841475877</v>
+      </c>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="n">
+        <v>0.2759358288770055</v>
+      </c>
+      <c r="AT24" t="n">
         <v>-0.06076203208556308</v>
       </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="n">
-        <v>11219179.47860963</v>
-      </c>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="n">
-        <v>3.738843781354603</v>
-      </c>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="n">
-        <v>3.612489841475877</v>
-      </c>
-      <c r="AS24" t="n">
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="n">
+        <v>0.3685337035287972</v>
+      </c>
+      <c r="AW24" t="n">
         <v>4.103810160427827</v>
       </c>
-      <c r="AT24" t="n">
-        <v>5037214.783328479</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.823930481283426</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>7.727606951871664</v>
-      </c>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
+      <c r="AX24" t="n">
+        <v>0.1663710649194801</v>
+      </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
-        <v>0.3685337035287972</v>
+        <v>5.16753648914441</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.2759358288770055</v>
+        <v>3.738843781354603</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.1663710649194801</v>
+        <v>5037214.783328479</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -3600,48 +3600,48 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="n">
-        <v>-1.38937364744487</v>
-      </c>
+      <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
+        <v>-3.242951574569247</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1210937.592840165</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.610386957813432</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="n">
+        <v>0.2419084777794467</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
+        <v>0.02723559120617947</v>
+      </c>
+      <c r="AT25" t="n">
         <v>-2.581517379679145</v>
       </c>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="n">
-        <v>-1210937.592840165</v>
-      </c>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="n">
-        <v>1.727642798253868</v>
-      </c>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="n">
-        <v>0.2419084777794467</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="n">
+        <v>-1.359994890304549</v>
+      </c>
+      <c r="AW25" t="n">
         <v>2.367082590611972</v>
       </c>
-      <c r="AT25" t="n">
-        <v>-86104.64801171096</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>-3.242951574569247</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.610386957813432</v>
-      </c>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
+      <c r="AX25" t="n">
+        <v>-0.06801543080613381</v>
+      </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
-        <v>-1.359994890304549</v>
+        <v>-1.38937364744487</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.02723559120617947</v>
+        <v>1.727642798253868</v>
       </c>
       <c r="BC25" t="n">
-        <v>-0.06801543080613381</v>
+        <v>-86104.64801171096</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -3726,48 +3726,48 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="n">
-        <v>0.02459947102754256</v>
-      </c>
+      <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>-1.222188995215312</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
+        <v>-0.1710227272727138</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>601281.5656565665</v>
+      </c>
       <c r="AN26" t="n">
-        <v>587120.2153110052</v>
+        <v>1.504924242424252</v>
       </c>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="n">
-        <v>0.3419504260465231</v>
-      </c>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="n">
-        <v>1.909436150472288</v>
-      </c>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="n">
+        <v>2.00227591199058</v>
+      </c>
+      <c r="AR26" t="inlineStr"/>
       <c r="AS26" t="n">
-        <v>2.600448564593307</v>
+        <v>0.04829545454545459</v>
       </c>
       <c r="AT26" t="n">
-        <v>402850.2249925842</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>-0.1901614832535898</v>
-      </c>
+        <v>-1.235479797979796</v>
+      </c>
+      <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="n">
-        <v>1.482595693779899</v>
-      </c>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
+        <v>-0.611086337173294</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.54223484848481</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.09306774897807513</v>
+      </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
-        <v>-0.6050718118223841</v>
+        <v>0.02289479592468524</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.04829545454545459</v>
+        <v>0.3001956108840176</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.09306774897807513</v>
+        <v>401234.4372574219</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -3852,48 +3852,48 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="n">
-        <v>-3.175670678764192</v>
-      </c>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
+        <v>-3.30828877005348</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1459212.56684492</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-3.782085561497325</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="n">
+        <v>1.497366639269558</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
         <v>0.4807486631016005</v>
       </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="n">
-        <v>-1459212.56684492</v>
-      </c>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="n">
-        <v>-1.439138831859267</v>
-      </c>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="n">
-        <v>1.497366639269558</v>
-      </c>
-      <c r="AS27" t="n">
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="n">
+        <v>-1.923622652973922</v>
+      </c>
+      <c r="AW27" t="n">
         <v>-1.80187165775402</v>
       </c>
-      <c r="AT27" t="n">
-        <v>-465633.0931885233</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>-3.30828877005348</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>-3.782085561497325</v>
-      </c>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
+      <c r="AX27" t="n">
+        <v>-0.04174125874125889</v>
+      </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
-        <v>-1.923622652973922</v>
+        <v>-3.175670678764192</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>-1.439138831859267</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.04174125874125889</v>
+        <v>-465633.0931885233</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -3974,48 +3974,48 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="n">
-        <v>11.42025415227688</v>
-      </c>
+      <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
+        <v>14.18502673796792</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>33994391.71122994</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.09010695187166</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="n">
+        <v>-2.225128889783576</v>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
+        <v>0.7219251336898393</v>
+      </c>
+      <c r="AT28" t="n">
         <v>0.6786096256684502</v>
       </c>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="n">
-        <v>33994391.71122994</v>
-      </c>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="n">
-        <v>9.396166424073627</v>
-      </c>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="n">
-        <v>-2.225128889783576</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>-2.316109625668474</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>14387367.21809869</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>14.18502673796792</v>
-      </c>
+      <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="n">
-        <v>12.09010695187166</v>
-      </c>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
+        <v>0.2701711468630705</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>-2.316109625668446</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.5886582085000445</v>
+      </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
-        <v>0.270171146863067</v>
+        <v>11.42025415227688</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.7219251336898393</v>
+        <v>9.396166424073627</v>
       </c>
       <c r="BC28" t="n">
-        <v>0.5886582085000445</v>
+        <v>14387367.21809869</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -4096,48 +4096,48 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="n">
-        <v>3.831704548550221</v>
-      </c>
+      <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>-1.58271531100479</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
+        <v>4.842882775119605</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>3294898.325358852</v>
+      </c>
       <c r="AN29" t="n">
-        <v>3294898.325358852</v>
+        <v>5.651495215311002</v>
       </c>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="n">
-        <v>3.212760426337368</v>
-      </c>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="n">
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="n">
         <v>3.384785940445283</v>
       </c>
+      <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="n">
+        <v>0.03977272727272729</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>-1.582715311004787</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>-0.02941303836112397</v>
+      </c>
+      <c r="AW29" t="n">
         <v>2.518899521531125</v>
       </c>
-      <c r="AT29" t="n">
-        <v>1588556.238894036</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.842882775119605</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>5.651495215311002</v>
-      </c>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
+      <c r="AX29" t="n">
+        <v>0.1616423155145981</v>
+      </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
-        <v>-0.02941303836112397</v>
+        <v>3.831704548550221</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.03977272727272729</v>
+        <v>3.212760426337368</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.1616423155145981</v>
+        <v>1588556.238894036</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -4222,48 +4222,48 @@
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>4.497844206348788</v>
-      </c>
+      <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>-0.8820987654321009</v>
-      </c>
-      <c r="AM30" t="inlineStr"/>
+        <v>2.039105763517526</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>552229.7979797977</v>
+      </c>
       <c r="AN30" t="n">
-        <v>540479.7979797977</v>
+        <v>2.93879382055853</v>
       </c>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="n">
-        <v>3.753297655296223</v>
-      </c>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="n">
-        <v>6.529332199381685</v>
-      </c>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="n">
+        <v>6.517959944870711</v>
+      </c>
+      <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="n">
-        <v>4.015953984287364</v>
+        <v>0.04168449197860991</v>
       </c>
       <c r="AT30" t="n">
-        <v>882722.8283380743</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>2.048995510662181</v>
-      </c>
+        <v>-0.9180629827688698</v>
+      </c>
+      <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="n">
-        <v>2.920179573512911</v>
-      </c>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
+        <v>1.435333938003033</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.072159833630451</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.09644191236927457</v>
+      </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
-        <v>1.476114748566122</v>
+        <v>4.402395637005341</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.03247474747474755</v>
+        <v>3.678550761634597</v>
       </c>
       <c r="BC30" t="n">
-        <v>0.09343772185734411</v>
+        <v>855568.5292396389</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -4340,48 +4340,48 @@
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="n">
-        <v>5.988729129077242</v>
-      </c>
+      <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
+        <v>5.821590909090915</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>6887034.090909091</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>8.0625</v>
+      </c>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="n">
+        <v>-2.230655978170063</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="n">
+        <v>0.2085227272727272</v>
+      </c>
+      <c r="AT31" t="n">
         <v>-3.419886363636365</v>
       </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="n">
-        <v>6887034.090909091</v>
-      </c>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="n">
-        <v>8.011850432176516</v>
-      </c>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="n">
-        <v>-2.230655978170063</v>
-      </c>
-      <c r="AS31" t="n">
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="n">
+        <v>0.04467148514141073</v>
+      </c>
+      <c r="AW31" t="n">
         <v>0.1647727272727195</v>
       </c>
-      <c r="AT31" t="n">
-        <v>3035013.213297925</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.821590909090915</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>8.0625</v>
-      </c>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
+      <c r="AX31" t="n">
+        <v>0.1930165193377336</v>
+      </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
-        <v>0.04467148514141073</v>
+        <v>5.988729129077242</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.2085227272727272</v>
+        <v>8.011850432176516</v>
       </c>
       <c r="BC31" t="n">
-        <v>0.1930165193377336</v>
+        <v>3035013.213297925</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -4466,48 +4466,48 @@
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="n">
-        <v>6.211630004234308</v>
-      </c>
+      <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
+        <v>7.469318181818167</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>5466605.113636363</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>8.40625</v>
+      </c>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="n">
+        <v>1.934981211672778</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
+        <v>0.1920454545454549</v>
+      </c>
+      <c r="AT32" t="n">
         <v>0.25</v>
       </c>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="n">
-        <v>5466605.113636363</v>
-      </c>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="n">
-        <v>5.923114692952453</v>
-      </c>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="n">
-        <v>1.934981211672778</v>
-      </c>
-      <c r="AS32" t="n">
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="n">
+        <v>0.6262389293239679</v>
+      </c>
+      <c r="AW32" t="n">
         <v>-0.7767045454545496</v>
       </c>
-      <c r="AT32" t="n">
-        <v>2679710.199527505</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.469318181818167</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>8.40625</v>
-      </c>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
+      <c r="AX32" t="n">
+        <v>0.3998641571527601</v>
+      </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
-        <v>0.6262389293239679</v>
+        <v>6.211630004234308</v>
       </c>
       <c r="BB32" t="n">
-        <v>0.1920454545454549</v>
+        <v>5.923114692952453</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.3998641571527601</v>
+        <v>2679710.199527505</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -4588,48 +4588,48 @@
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="n">
-        <v>6.150198322393763</v>
-      </c>
+      <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
+        <v>6.701552287581706</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>4741418.690582294</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>7.521397801544865</v>
+      </c>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="n">
+        <v>1.446727699068305</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
+        <v>0.1877005347593583</v>
+      </c>
+      <c r="AT33" t="n">
         <v>-0.5787098930481314</v>
       </c>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="n">
-        <v>4741418.690582294</v>
-      </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="n">
-        <v>7.832641138358738</v>
-      </c>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="n">
-        <v>1.446727699068362</v>
-      </c>
-      <c r="AS33" t="n">
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="n">
+        <v>-0.3668309840014814</v>
+      </c>
+      <c r="AW33" t="n">
         <v>2.62128639334523</v>
       </c>
-      <c r="AT33" t="n">
-        <v>3125642.18425308</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.701552287581706</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>7.521397801544865</v>
-      </c>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
+      <c r="AX33" t="n">
+        <v>0.1450539938678224</v>
+      </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
-        <v>-0.3668309840014814</v>
+        <v>6.150198322393763</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.1877005347593583</v>
+        <v>7.832641138358738</v>
       </c>
       <c r="BC33" t="n">
-        <v>0.1450539938678224</v>
+        <v>3125642.18425308</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>45508.64583333334</v>
       </c>
       <c r="C34" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D34" t="n">
         <v>34</v>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M34" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N34" t="n">
         <v>-1</v>
@@ -4743,7 +4743,7 @@
         <v>45508.54166666666</v>
       </c>
       <c r="C35" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D35" t="n">
         <v>72</v>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M35" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
@@ -4841,7 +4841,7 @@
         <v>45507.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" t="n">
         <v>86</v>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M36" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -4935,7 +4935,7 @@
         <v>45507.54166666666</v>
       </c>
       <c r="C37" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D37" t="n">
         <v>86</v>
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M37" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>

--- a/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD37"/>
+  <dimension ref="A1:BB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,262 +450,252 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -725,113 +715,109 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>187</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>77</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>771</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>243</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>80</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>5.137752525252495</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.1189213564213567</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9.273250360750339</v>
+      </c>
+      <c r="V2" t="n">
+        <v>26730865.8008658</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5399331691276772</v>
+      </c>
+      <c r="X2" t="n">
+        <v>10.47252886002885</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5549742282465218</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.7450757575757576</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.085918603347665</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13809076.69498694</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6.596242594044668</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.345127149272454</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>68.04278074866309</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>9.089746145667178</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26316441.30449229</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.42765483785222</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>0.8078586605513181</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0.7171384901648059</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.2942351143008999</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-0.9420320676891656</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.410778841042003</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.5459072484189291</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>6.640485751307722</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.917128189413802</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>12028605.38995147</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -849,115 +835,113 @@
         <v>84</v>
       </c>
       <c r="E3" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F3" t="n">
         <v>40</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>30</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>77</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>771</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>102</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>239</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>-7</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-2.752479338842988</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.766735537190087</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-6.257851239669421</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-13718440.08264463</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.2947911750085661</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-3.877479338842974</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-3.394648479174151</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.5239669421487605</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-4.0347488015571</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-10822359.77262197</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-6.790306286086903</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-2.161241373543746</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
-        <v>-6.033030303030287</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-13744621.21212121</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-4.183636363636367</v>
-      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>-4.055434497064908</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>-0.5093939393939393</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-1.495757575757573</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-2.229299625495273</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-3.216212121212152</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.3283421602552039</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>-6.671074826944377</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-3.890209040556869</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-10568611.85975659</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -975,115 +959,113 @@
         <v>85</v>
       </c>
       <c r="E4" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F4" t="n">
         <v>64</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>202</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>77</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>771</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>241</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>250</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>-13</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>-4</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>-2</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1.697727272727207</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.168181818181818</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-6.572727272727278</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-18103636.36363636</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.8100739617980994</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-4.57386363636364</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.02284171368222587</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.9477272727272728</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-6.339558641390525</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-14254208.26930094</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-6.128442881352356</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6009995193184814</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="n">
-        <v>-6.702840909090895</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-18640000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-5.069886363636357</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>0.7349502608662135</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>-0.9857954545454541</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1.088636363636361</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>0.9030359248031665</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.419886363636294</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-0.7665050068067309</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>-5.733964776044502</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-6.257788860644467</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-13505627.90843017</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1101,117 +1083,113 @@
         <v>55</v>
       </c>
       <c r="E5" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F5" t="n">
         <v>66</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>74</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>77</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>771</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>121</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>151</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>-0.8743801652892955</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.855463728191001</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7.525068870523413</v>
+      </c>
+      <c r="V5" t="n">
+        <v>15189251.60697888</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7337142148854234</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.239210284664836</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.3014113012552855</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.7323232323232323</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.218498831758652</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14304179.26118215</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.971793864550278</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6626653311092667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>66.74171122994652</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>7.863662945241899</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>15854971.42477406</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5.371477937267429</v>
-      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>0.7789190073646353</v>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>0.7714513556618818</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.100744284954811</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>0.418222312594466</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.928681552365731</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.7624276563694841</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>8.902841571505405</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.525515764174813</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14298237.45558041</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1223,49 +1201,49 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D6" t="n">
         <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>23860</v>
       </c>
       <c r="F6" t="n">
         <v>135</v>
       </c>
       <c r="G6" t="n">
+        <v>135</v>
+      </c>
+      <c r="H6" t="n">
         <v>77</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>774</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>244</v>
-      </c>
       <c r="M6" t="n">
-        <v>256</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>247</v>
+      </c>
+      <c r="N6" t="n">
+        <v>259</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1278,7 +1256,9 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1302,10 +1282,6 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1320,110 +1296,106 @@
         <v>126</v>
       </c>
       <c r="D7" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" t="n">
         <v>87</v>
       </c>
-      <c r="E7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F7" t="n">
-        <v>87</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>77</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>774</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>142</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>48</v>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-5.279090909090911</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.117954545454548</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-5.819090909090903</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-4028488.636363637</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1314215290096099</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-6.969090909090909</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-5.569708202578141</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.2147727272727273</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-6.471429843360312</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2776084.917026446</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-4.777819365243843</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.443403829976734</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="n">
-        <v>-6.015142133408389</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-4609838.164931045</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-6.88097382493666</v>
-      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>-5.500366320648908</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>-0.1877005347593583</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.299493385871099</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>0.7834117404134737</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-5.247509147199594</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.1450539938678224</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-4.944922616898523</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-5.97127180757721</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-2941683.127128219</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1435,49 +1407,49 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F8" t="n">
         <v>20</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>199</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>77</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>774</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>54</v>
       </c>
-      <c r="M8" t="n">
-        <v>256</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>259</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1490,7 +1462,9 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1514,10 +1488,6 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1535,113 +1505,109 @@
         <v>21</v>
       </c>
       <c r="E9" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F9" t="n">
         <v>111</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>157</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>77</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>774</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>194</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0.5363636363636886</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4420454545454575</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.85227272727272</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2042386.363636364</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1631535326241038</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.18295454545455</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.887576817189796</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.1522727272727273</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.3112512524114948</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>153377.3845989867</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.031120537886963</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.457437235416108</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
-        <v>67.19374999999999</v>
-      </c>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
-        <v>2.951537433155096</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>2247004.512032086</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.614739304812815</v>
-      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>1.244206442043776</v>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>-0.1197860962566846</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.3389037433155089</v>
-      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>-0.9320520145106528</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.5141042780749103</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.1189944134511529</v>
-      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>0.3695790458458816</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.9079894194025684</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>383576.1582915769</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1659,115 +1625,113 @@
         <v>77</v>
       </c>
       <c r="E10" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F10" t="n">
         <v>110</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>65</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>77</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>774</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>67</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>151</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-1</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>-3.335196117014306</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.4609996064541484</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.218273645546375</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-573281.5164633342</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.1231447735400304</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.500721500721482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.154538892523107</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.08512396694214885</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1611064532013131</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-634151.1288265241</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-3.178571065883318</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-3.308291113073718</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="n">
-        <v>-1.75121212121212</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-588303.6616161615</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1.69123737373738</v>
-      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>-3.580308104541672</v>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>-0.07590909090909093</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.8690656565656525</v>
-      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-2.784582644609817</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-3.507045454545505</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.1332755740636173</v>
-      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>-2.747912194101971</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-0.176951640729385</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-606405.7201754248</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1785,115 +1749,113 @@
         <v>67</v>
       </c>
       <c r="E11" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>175</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>77</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>771</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>223</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>34</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-8</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>-1.670454545454561</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.2272727272727302</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.818181818181827</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6197727.272727272</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1214716872602266</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.39772727272728</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.863865511132303</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2272727272727275</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.347507658088276</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3729395.905956695</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.4948934508227154</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.273305940781857</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
-        <v>2.274732620320862</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>7252874.331550803</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.074197860962585</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>1.889210406311065</v>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>0.237967914438503</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-0.5143716577540118</v>
-      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-2.066770350123548</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-1.203877005347607</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.1266443574924809</v>
-      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="n">
-        <v>0.4328779247478565</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.010630475001662</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3729855.911497741</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1911,115 +1873,113 @@
         <v>49</v>
       </c>
       <c r="E12" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F12" t="n">
         <v>116</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>21</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>77</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>771</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>124</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>100</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-16</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-5</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-3</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1.436363636363609</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.209090909090911</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-7.836363636363657</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-31189602.27272727</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.480748113971798</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-6.047727272727272</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.07267263860723</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.5874999999999997</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-3.799755194782279</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-12658761.62263304</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-5.189861179412262</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.7889116065393154</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="n">
-        <v>-7.571390374331557</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-30368397.39304812</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-5.760561497326194</v>
-      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="n">
-        <v>1.97728673630715</v>
-      </c>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="n">
-        <v>-0.5741978609625664</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-1.320655080213903</v>
-      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>-0.9825383834065065</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.270655080213885</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-0.556664160880997</v>
-      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="n">
-        <v>-5.58431113515968</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-4.029185113685571</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-12165343.01276696</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1</v>
-      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2037,115 +1997,113 @@
         <v>41</v>
       </c>
       <c r="E13" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F13" t="n">
         <v>23</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>72</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>77</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>771</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>36</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>16</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>20</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>20</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>-1.834217171717171</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.5242424242424235</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.020707070707076</v>
+      </c>
+      <c r="V13" t="n">
+        <v>19151470.95959596</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.3207038962069921</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.528914141414148</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1954370250277293</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.5503787878787878</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.236519588011447</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16330589.09981917</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.203836320162765</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.6596914672659615</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="n">
-        <v>5.090968508615575</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>23500448.0466429</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>5.320372846108143</v>
-      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>-1.387046487923982</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="n">
-        <v>0.5912990196078429</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-0.4201091800356487</v>
-      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
-        <v>-0.09092325841835347</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-1.489100564468174</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.366565033804662</v>
-      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="n">
-        <v>4.334612890075178</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.591040922889363</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14102815.94335211</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2163,117 +2121,113 @@
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>16284</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>15</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>77</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>771</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>99</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>23</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0.3852272727272918</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.005681818181816567</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.019318181818178</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-2847727.272727272</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1575027649484173</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.532954545454572</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.09437078621863293</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.3193181818181818</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.972126842561607</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1084997.819838173</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.441979802604806</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.631120334979034</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="n">
-        <v>67.53779904306221</v>
-      </c>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="n">
-        <v>-1.356250000000003</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-3345568.181818182</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-1.802840909090904</v>
-      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="n">
-        <v>0.05417472090073261</v>
-      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="n">
-        <v>-0.3164772727272729</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-0.1630681818181792</v>
-      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="n">
-        <v>0.006451685669258467</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.01420454545456096</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-0.07699647959486788</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="n">
-        <v>-1.257029460488994</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-2.323626768762622</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>-1190955.770298091</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2291,117 +2245,113 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F15" t="n">
         <v>126</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>178</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>77</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>774</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>83</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>38</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-1</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-1.425108225108175</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.07748917748918061</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.9748917748917592</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-144906.2049062047</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1146631146631145</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.4891774891774929</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2.460494782994829</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.1047619047619048</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.4465687883544973</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>209588.2817579245</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.470945654874228</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.645089407946553</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="n">
-        <v>72.08440656565656</v>
-      </c>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="n">
-        <v>-1.129861111111126</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>-171476.0890151518</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-0.3231060606060652</v>
-      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="n">
-        <v>-2.111835675633642</v>
-      </c>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="n">
-        <v>-0.05912247474747478</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-0.3915719696969724</v>
-      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="n">
-        <v>2.578750476894065</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-0.3889520202020265</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.136952686001599</v>
-      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="n">
-        <v>2.40815014573738</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-0.2481200292445322</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>167732.1259982996</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2413,53 +2363,53 @@
         <v>45521.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D16" t="n">
         <v>76</v>
       </c>
       <c r="E16" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F16" t="n">
         <v>133</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>137</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>77</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>774</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>196</v>
       </c>
-      <c r="M16" t="n">
-        <v>256</v>
-      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
+        <v>259</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2472,7 +2422,9 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2496,10 +2448,6 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2517,117 +2465,113 @@
         <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>5539</v>
       </c>
       <c r="F17" t="n">
         <v>69</v>
       </c>
       <c r="G17" t="n">
+        <v>69</v>
+      </c>
+      <c r="H17" t="n">
         <v>77</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>774</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>154</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>147</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-4</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-1</v>
       </c>
       <c r="Q17" t="n">
         <v>-1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.9753246753246572</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.455844155844161</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5909090909090935</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-281123.3766233767</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.03588935908811708</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.5727272727272776</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.659728467989339</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1571428571428573</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.9711973648619505</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-30343.84931263793</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.105598955909514</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8013587757997769</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="n">
-        <v>80.77593582887701</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="n">
-        <v>1.324431818181807</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-217602.2727272725</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-0.3562499999999886</v>
-      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="n">
-        <v>1.853407486577538</v>
-      </c>
+      <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="n">
-        <v>0.1477272727272729</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.122727272727275</v>
-      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="n">
-        <v>0.3483848550646336</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>-0.457386363636374</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.04562227577173239</v>
-      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="n">
-        <v>0.4896370535558106</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-1.180634277023728</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-87083.34236664465</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2645,119 +2589,109 @@
         <v>17</v>
       </c>
       <c r="E18" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F18" t="n">
         <v>53</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>43</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>77</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>774</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>36</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>31</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-2</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>1.591684704184729</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2825216450216459</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.575054112554099</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1929656.385281385</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.2106879614193855</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.17613636363636</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4400401392921083</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.3265151515151514</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.561950199905752</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2130819.998786534</v>
+      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.379412618071399</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr"/>
+        <v>-0.06794419829028442</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="n">
-        <v>73.5529411764706</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>68.32361111111112</v>
-      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="n">
-        <v>5.233017676767673</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>2406376.262626262</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6.735164141414145</v>
-      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="n">
-        <v>0.6666001861737527</v>
-      </c>
+      <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="n">
-        <v>0.4115530303030304</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.1240530303030276</v>
-      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="n">
-        <v>0.05847053866046181</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.2901515151515071</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.22161293970963</v>
-      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="n">
-        <v>5.551435295197905</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.541808330516318</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2633790.748537584</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2775,115 +2709,111 @@
         <v>36</v>
       </c>
       <c r="E19" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F19" t="n">
         <v>17</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>84</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>77</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>771</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>54</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>239</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>-4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-1</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>1.200389610389635</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.565324675324678</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-6.719480519480527</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-9618805.194805196</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.4653025480544217</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-4.187532467532463</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.665251358752812</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.5484415584415583</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-5.676065365058619</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-9149322.650899824</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-6.244488243973251</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.04407209978649007</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="n">
-        <v>70.45454545454544</v>
-      </c>
+      <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="n">
-        <v>-6.266477272727286</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>-9621925.505050506</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>-3.93093434343433</v>
-      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="n">
-        <v>2.800631015993559</v>
-      </c>
+      <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="n">
-        <v>-0.6259469696969695</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>-1.552651515151517</v>
-      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
       <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="n">
-        <v>-0.600895325968029</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.952335858585855</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>-0.4535389413040143</v>
-      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="n">
-        <v>-6.316178798218132</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-5.380076571829122</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>-9133775.147276189</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2901,117 +2831,113 @@
         <v>48</v>
       </c>
       <c r="E20" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F20" t="n">
         <v>79</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>63</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>77</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>771</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>serie a</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>223</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>189</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-19</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-2</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>1.220454545454572</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.927272727272729</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-9.746590909090912</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-32638892.04545454</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.5871377026284312</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-7.047727272727286</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.478937175948062</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.181818181818182</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-7.428792979008762</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-19940126.21675621</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-8.970682125786013</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.064166324463638</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="n">
-        <v>65.97727272727273</v>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="n">
-        <v>-9.40741978609627</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>-33358871.15641712</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-6.972727272727269</v>
-      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="n">
-        <v>1.32295656964817</v>
-      </c>
+      <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="n">
-        <v>-1.236831550802138</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>-1.695320855614973</v>
-      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
       <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="n">
-        <v>-0.4467515755119642</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.342780748663102</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>-0.5178998993836745</v>
-      </c>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="n">
-        <v>-8.228429759785669</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>-7.329428557376104</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>-20278688.94379877</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -3029,123 +2955,113 @@
         <v>51</v>
       </c>
       <c r="E21" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F21" t="n">
         <v>94</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>153</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>77</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>774</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>162</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>240</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-5</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.3840909090909861</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.7386363636363598</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-3.072727272727263</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1077357.954545455</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-3.125</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.2055993214473233</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-2.204454930654336</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-869664.7429776408</v>
+      </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>-4.581173248464282</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr"/>
+        <v>-2.065331805632592</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="n">
-        <v>70.28352272727273</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>70.05</v>
-      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="n">
-        <v>-3.712834224598922</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>-1227760.546642899</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-3.335115864527623</v>
-      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="n">
-        <v>0.2975194663137017</v>
-      </c>
+      <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>-0.6808674985145586</v>
-      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
       <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="n">
-        <v>-1.261373382115956</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.1329768270944101</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="n">
-        <v>-4.027486597145312</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>-2.739322588789406</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>-819851.9671755133</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -3163,115 +3079,113 @@
         <v>17</v>
       </c>
       <c r="E22" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F22" t="n">
         <v>53</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>178</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>77</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>773</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>36</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>38</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-4</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1.931367243867271</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1650974025974037</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.70203823953824</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1462473.845598846</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.2106879614193855</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.187247474747466</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.6564889268798311</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.2217532467532466</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.896107590134577</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2022559.271616879</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.639715133016765</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8801902069869776</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
-        <v>3.760795454545445</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1979628.708964646</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>4.605934343434342</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="n">
-        <v>0.398779474038804</v>
-      </c>
+      <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="n">
-        <v>0.3035669191919192</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.2040719696969688</v>
-      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="n">
-        <v>0.8696428223105741</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.011931818181807</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.22161293970963</v>
-      </c>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="n">
-        <v>6.089047780125895</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.087420648332937</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2533885.095720999</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -3289,115 +3203,113 @@
         <v>21</v>
       </c>
       <c r="E23" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F23" t="n">
         <v>111</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>180</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>77</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>773</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>194</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>73</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>3</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>2.928571428571416</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.710714285714285</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.52402597402596</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2787727.272727272</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.1146631146631145</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.510389610389609</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.686402286563492</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.230070082930837</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1207378.704094783</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.7487109312962019</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-3.395083739765152</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="n">
-        <v>3.800568181818193</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>2985852.272727273</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>4.928409090909085</v>
-      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="n">
-        <v>2.766901967417368</v>
-      </c>
+      <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="n">
-        <v>-0.04886363636363633</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>-1.805113636363636</v>
-      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="n">
-        <v>-3.394296391025684</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.984090909090924</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>-0.136952686001599</v>
-      </c>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="n">
-        <v>1.165836514289481</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.511101033142836</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1321688.811256158</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -3415,111 +3327,109 @@
         <v>56</v>
       </c>
       <c r="E24" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F24" t="n">
         <v>51</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>165</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>77</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>773</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>63</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>80</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>8</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>3.912824675324714</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4803571428571445</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8.069318181818176</v>
+      </c>
+      <c r="V24" t="n">
+        <v>12203165.58441558</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2191846874315915</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.230519480519462</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.615569283478578</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.2352272727272728</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.821433199941325</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>4143985.203192633</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.160803484477043</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.023828117652613</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="n">
-        <v>7.823930481283426</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>11219179.47860963</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>7.727606951871664</v>
-      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="n">
-        <v>3.612489841475877</v>
-      </c>
+      <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="n">
-        <v>0.2759358288770055</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>-0.06076203208556308</v>
-      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
       <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="n">
-        <v>0.3685337035287972</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.103810160427827</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0.1663710649194801</v>
-      </c>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="n">
-        <v>5.16753648914441</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.738843781354603</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5037214.783328479</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3537,115 +3447,113 @@
         <v>48</v>
       </c>
       <c r="E25" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F25" t="n">
         <v>103</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>187</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>77</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>773</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>228</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>80</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>-1</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>2.913131313131288</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-2.158820346320351</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-2.825360750360758</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1099803.391053391</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.08479111532054406</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.825559163059154</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.3672755378237014</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.1078282828282828</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.403595357616354</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-243800.5675060903</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-1.33220168284997</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-1.64982321652575</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="n">
-        <v>-3.242951574569247</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>-1210937.592840165</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.610386957813432</v>
-      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="n">
-        <v>0.2419084777794467</v>
-      </c>
+      <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="n">
-        <v>0.02723559120617947</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>-2.581517379679145</v>
-      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="n">
-        <v>-1.359994890304549</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.367082590611972</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>-0.06801543080613381</v>
-      </c>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="n">
-        <v>-1.38937364744487</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.727642798253868</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>-86104.64801171096</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3663,115 +3571,113 @@
         <v>36</v>
       </c>
       <c r="E26" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F26" t="n">
         <v>17</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>153</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>77</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>773</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>54</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>240</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>7</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1.537662337662312</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.6025974025974</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.7558441558441586</v>
+      </c>
+      <c r="V26" t="n">
+        <v>419285.7142857141</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1064991771513513</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9961038961038895</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.707428597972068</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.06883116883116891</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.1382925448142913</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>338386.3462423247</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.05710520960519716</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-0.4041245067332007</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="n">
-        <v>-0.1710227272727138</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>601281.5656565665</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.504924242424252</v>
-      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="n">
-        <v>2.00227591199058</v>
-      </c>
+      <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="n">
-        <v>0.04829545454545459</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>-1.235479797979796</v>
-      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
       <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="n">
-        <v>-0.611086337173294</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.54223484848481</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0.09306774897807513</v>
-      </c>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="n">
-        <v>0.02289479592468524</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0.3001956108840176</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>401234.4372574219</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3789,115 +3695,113 @@
         <v>51</v>
       </c>
       <c r="E27" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F27" t="n">
         <v>94</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>74</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>77</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>773</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>162</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>151</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-1</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>-1.949380165289284</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.6663223140495873</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-2.617355371900814</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1349672.004132232</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.0360203432930708</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-3.351446280991738</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.2937520635229589</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-1.178873265211024</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-474531.2390035735</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-3.484680887436355</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-2.147897146893587</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="n">
-        <v>-3.30828877005348</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>-1459212.56684492</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>-3.782085561497325</v>
-      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="n">
-        <v>1.497366639269558</v>
-      </c>
+      <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.4807486631016005</v>
-      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="n">
-        <v>-1.923622652973922</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>-1.80187165775402</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>-0.04174125874125889</v>
-      </c>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="n">
-        <v>-3.175670678764192</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>-1.439138831859267</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>-465633.0931885233</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -3915,111 +3819,109 @@
         <v>33</v>
       </c>
       <c r="E28" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F28" t="n">
         <v>15</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>69</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>77</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>773</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>102</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>147</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>-1.848701298701286</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.2292207792207748</v>
+      </c>
+      <c r="U28" t="n">
+        <v>13.52792207792209</v>
+      </c>
+      <c r="V28" t="n">
+        <v>34549058.44155844</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.5265483785220626</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.0461038961039</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-2.702244859864209</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>9.457919826762918</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>15048306.9673806</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.61543115866236</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.4528896527339796</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="n">
-        <v>14.18502673796792</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>33994391.71122994</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>12.09010695187166</v>
-      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="n">
-        <v>-2.225128889783576</v>
-      </c>
+      <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="n">
-        <v>0.7219251336898393</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.6786096256684502</v>
-      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
       <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="n">
-        <v>0.2701711468630705</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>-2.316109625668446</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0.5886582085000445</v>
-      </c>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="n">
-        <v>11.42025415227688</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.396166424073627</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>14387367.21809869</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -4037,111 +3939,109 @@
         <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>16284</v>
       </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>58</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>77</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>773</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>99</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>171</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>2.320000000000022</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-1.325909090909093</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.955454545454543</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3226954.545454546</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1336487586487585</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.725909090909084</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.631591769341782</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.03409090909090917</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.221840446590448</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1860737.445424945</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.963576368076374</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-0.6765201095201121</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="n">
-        <v>4.842882775119605</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>3294898.325358852</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>5.651495215311002</v>
-      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="n">
-        <v>3.384785940445283</v>
-      </c>
+      <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="n">
-        <v>0.03977272727272729</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>-1.582715311004787</v>
-      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="n">
-        <v>-0.02941303836112397</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.518899521531125</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.1616423155145981</v>
-      </c>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="n">
-        <v>3.831704548550221</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>3.212760426337368</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1588556.238894036</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -4159,115 +4059,113 @@
         <v>40</v>
       </c>
       <c r="E30" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F30" t="n">
         <v>47</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>193</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>77</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>773</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>38</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>91</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-8</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>-3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>-1</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>4.714304662789488</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-1.108825630037753</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.700204060810123</v>
+      </c>
+      <c r="V30" t="n">
+        <v>699320.4775022955</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.1231447735400304</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.847025813692468</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>6.904574959515656</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.08512396694214885</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.53772168981655</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>865610.5606185647</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.002679919992175</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.165032021118975</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="n">
-        <v>2.039105763517526</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>552229.7979797977</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.93879382055853</v>
-      </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="n">
-        <v>6.517959944870711</v>
-      </c>
+      <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="n">
-        <v>0.04168449197860991</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>-0.9180629827688698</v>
-      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="n">
-        <v>1.435333938003033</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.072159833630451</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0.09644191236927457</v>
-      </c>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="n">
-        <v>4.402395637005341</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>3.678550761634597</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>855568.5292396389</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -4285,107 +4183,105 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
+        <v>16917</v>
+      </c>
+      <c r="F31" t="n">
         <v>9</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>106</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>77</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>773</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>243</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>240</v>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0.1777597402597166</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-3.34301948051948</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5.619967532467527</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6306772.727272728</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2552621645090587</v>
+      </c>
+      <c r="X31" t="n">
+        <v>7.558603896103918</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-2.887619158216978</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.1962662337662338</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.155626252916619</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3135098.336140941</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.175921114915681</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.3646378043971197</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="n">
-        <v>5.821590909090915</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>6887034.090909091</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>8.0625</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="n">
-        <v>-2.230655978170063</v>
-      </c>
+      <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="n">
-        <v>0.2085227272727272</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>-3.419886363636365</v>
-      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="n">
-        <v>0.04467148514141073</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0.1647727272727195</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0.1930165193377336</v>
-      </c>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="n">
-        <v>5.988729129077242</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8.011850432176516</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>3035013.213297925</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -4403,115 +4299,113 @@
         <v>48</v>
       </c>
       <c r="E32" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F32" t="n">
         <v>79</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>28</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>77</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>773</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>223</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>196</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>5</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>0.08376623376625503</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.1112012987012996</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7.290584415584419</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4940179.383116883</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.3309646358543419</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8.510227272727278</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.553664596273279</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.1988636363636365</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>5.897947168927047</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2309020.077770517</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.719531615786423</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.2736907299151525</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="n">
-        <v>7.469318181818167</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>5466605.113636363</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>8.40625</v>
-      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="n">
-        <v>1.934981211672778</v>
-      </c>
+      <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="n">
-        <v>0.1920454545454549</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="n">
-        <v>0.6262389293239679</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>-0.7767045454545496</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.3998641571527601</v>
-      </c>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="n">
-        <v>6.211630004234308</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>5.923114692952453</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2679710.199527505</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -4529,169 +4423,167 @@
         <v>10</v>
       </c>
       <c r="E33" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F33" t="n">
         <v>57</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>43</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>77</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>773</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>121</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>31</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>3.372871572871588</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.2991883116883116</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6.603968253968247</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4094492.243867244</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.1314215290096099</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.810101010101008</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.694985853498622</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2147727272727273</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7.897352830426158</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2933482.377502478</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.231971181681374</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.7053242481828654</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="n">
-        <v>6.701552287581706</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>4741418.690582294</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>7.521397801544865</v>
-      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="n">
-        <v>1.446727699068305</v>
-      </c>
+      <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="n">
-        <v>0.1877005347593583</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>-0.5787098930481314</v>
-      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
       <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="n">
-        <v>-0.3668309840014814</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.62128639334523</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.1450539938678224</v>
-      </c>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="n">
-        <v>6.150198322393763</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>7.832641138358738</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3125642.18425308</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45508.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D34" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>135</v>
+        <v>26000</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G34" t="n">
+        <v>137</v>
+      </c>
+      <c r="H34" t="n">
         <v>77</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>773</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>244</v>
-      </c>
       <c r="M34" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -4704,7 +4596,9 @@
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -4728,68 +4622,64 @@
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C35" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>87</v>
+        <v>23860</v>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
         <v>77</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>773</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>244</v>
-      </c>
       <c r="M35" t="n">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="N35" t="n">
+        <v>259</v>
+      </c>
+      <c r="O35" t="n">
         <v>-1</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -4802,7 +4692,9 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -4826,10 +4718,6 @@
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -4841,49 +4729,49 @@
         <v>45507.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D36" t="n">
         <v>86</v>
       </c>
       <c r="E36" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F36" t="n">
         <v>142</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>199</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>77</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>773</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>244</v>
-      </c>
       <c r="M36" t="n">
-        <v>256</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>247</v>
+      </c>
+      <c r="N36" t="n">
+        <v>259</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -4896,7 +4784,9 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -4920,10 +4810,6 @@
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -4935,49 +4821,49 @@
         <v>45507.54166666666</v>
       </c>
       <c r="C37" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D37" t="n">
         <v>86</v>
       </c>
       <c r="E37" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F37" t="n">
         <v>86</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>17</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>77</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>773</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>244</v>
-      </c>
       <c r="M37" t="n">
-        <v>256</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>247</v>
+      </c>
+      <c r="N37" t="n">
+        <v>259</v>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -4990,7 +4876,9 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -5014,10 +4902,6 @@
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr"/>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
